--- a/SH1002 intensities.xlsx
+++ b/SH1002 intensities.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680+ R1 airyscan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680+ R3 airyscan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R1 airyscan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R2 airyscan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R3 airyscan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680+ R1 airy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680+ R2 airy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680+ R3 airy" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R1 airy" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R2 airy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1002-gfp Ebba680- R3 airy" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1069,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8633916</v>
+        <v>8870043</v>
       </c>
       <c r="C2" t="n">
-        <v>1666403</v>
+        <v>1988518</v>
       </c>
     </row>
     <row r="3">
@@ -1080,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8915648</v>
+        <v>8843665</v>
       </c>
       <c r="C3" t="n">
-        <v>1600976</v>
+        <v>1901699</v>
       </c>
     </row>
     <row r="4">
@@ -1091,10 +1092,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8984205</v>
+        <v>9067964</v>
       </c>
       <c r="C4" t="n">
-        <v>1609087</v>
+        <v>1891993</v>
       </c>
     </row>
     <row r="5">
@@ -1102,10 +1103,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9111980</v>
+        <v>9294128</v>
       </c>
       <c r="C5" t="n">
-        <v>1617339</v>
+        <v>1934160</v>
       </c>
     </row>
     <row r="6">
@@ -1113,10 +1114,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9313645</v>
+        <v>9790397</v>
       </c>
       <c r="C6" t="n">
-        <v>1627938</v>
+        <v>1967930</v>
       </c>
     </row>
     <row r="7">
@@ -1124,10 +1125,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9340130</v>
+        <v>10259115</v>
       </c>
       <c r="C7" t="n">
-        <v>1625599</v>
+        <v>2006134</v>
       </c>
     </row>
     <row r="8">
@@ -1135,10 +1136,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9511997</v>
+        <v>10307167</v>
       </c>
       <c r="C8" t="n">
-        <v>1625969</v>
+        <v>2070916</v>
       </c>
     </row>
     <row r="9">
@@ -1146,10 +1147,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9885746</v>
+        <v>10602977</v>
       </c>
       <c r="C9" t="n">
-        <v>1650609</v>
+        <v>2103813</v>
       </c>
     </row>
     <row r="10">
@@ -1157,10 +1158,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9893157</v>
+        <v>10933283</v>
       </c>
       <c r="C10" t="n">
-        <v>1678082</v>
+        <v>2135093</v>
       </c>
     </row>
     <row r="11">
@@ -1168,10 +1169,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10161888</v>
+        <v>11234510</v>
       </c>
       <c r="C11" t="n">
-        <v>1698929</v>
+        <v>2203844</v>
       </c>
     </row>
     <row r="12">
@@ -1179,10 +1180,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10548696</v>
+        <v>11693686</v>
       </c>
       <c r="C12" t="n">
-        <v>1745791</v>
+        <v>2278719</v>
       </c>
     </row>
     <row r="13">
@@ -1190,10 +1191,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10987637</v>
+        <v>12074200</v>
       </c>
       <c r="C13" t="n">
-        <v>1806375</v>
+        <v>2358340</v>
       </c>
     </row>
     <row r="14">
@@ -1201,10 +1202,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11353979</v>
+        <v>12918852</v>
       </c>
       <c r="C14" t="n">
-        <v>1862881</v>
+        <v>2467185</v>
       </c>
     </row>
     <row r="15">
@@ -1212,10 +1213,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11695615</v>
+        <v>13683108</v>
       </c>
       <c r="C15" t="n">
-        <v>1926638</v>
+        <v>2579832</v>
       </c>
     </row>
     <row r="16">
@@ -1223,10 +1224,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12033428</v>
+        <v>14347710</v>
       </c>
       <c r="C16" t="n">
-        <v>1949778</v>
+        <v>2670686</v>
       </c>
     </row>
     <row r="17">
@@ -1234,10 +1235,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12461227</v>
+        <v>14996889</v>
       </c>
       <c r="C17" t="n">
-        <v>1988555</v>
+        <v>2761393</v>
       </c>
     </row>
     <row r="18">
@@ -1245,10 +1246,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12922532</v>
+        <v>15790554</v>
       </c>
       <c r="C18" t="n">
-        <v>2040761</v>
+        <v>2845693</v>
       </c>
     </row>
     <row r="19">
@@ -1256,10 +1257,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13567693</v>
+        <v>16373102</v>
       </c>
       <c r="C19" t="n">
-        <v>2126196</v>
+        <v>2936802</v>
       </c>
     </row>
     <row r="20">
@@ -1267,10 +1268,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14482095</v>
+        <v>17403676</v>
       </c>
       <c r="C20" t="n">
-        <v>2221151</v>
+        <v>3025387</v>
       </c>
     </row>
     <row r="21">
@@ -1278,10 +1279,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15417124</v>
+        <v>18699050</v>
       </c>
       <c r="C21" t="n">
-        <v>2312595</v>
+        <v>3191987</v>
       </c>
     </row>
     <row r="22">
@@ -1289,10 +1290,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>16394095</v>
+        <v>20676842</v>
       </c>
       <c r="C22" t="n">
-        <v>2412321</v>
+        <v>3415549</v>
       </c>
     </row>
     <row r="23">
@@ -1300,10 +1301,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>17326904</v>
+        <v>23356418</v>
       </c>
       <c r="C23" t="n">
-        <v>2512685</v>
+        <v>3724095</v>
       </c>
     </row>
     <row r="24">
@@ -1311,10 +1312,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>17696847</v>
+        <v>26780101</v>
       </c>
       <c r="C24" t="n">
-        <v>2565366</v>
+        <v>4062908</v>
       </c>
     </row>
     <row r="25">
@@ -1322,10 +1323,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>18846278</v>
+        <v>30459454</v>
       </c>
       <c r="C25" t="n">
-        <v>2629935</v>
+        <v>4357178</v>
       </c>
     </row>
     <row r="26">
@@ -1333,10 +1334,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>19845142</v>
+        <v>34089375</v>
       </c>
       <c r="C26" t="n">
-        <v>2724586</v>
+        <v>4646745</v>
       </c>
     </row>
     <row r="27">
@@ -1344,10 +1345,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>21283711</v>
+        <v>38741181</v>
       </c>
       <c r="C27" t="n">
-        <v>2807683</v>
+        <v>4971415</v>
       </c>
     </row>
     <row r="28">
@@ -1355,10 +1356,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>22847723</v>
+        <v>45281427</v>
       </c>
       <c r="C28" t="n">
-        <v>2976692</v>
+        <v>5405356</v>
       </c>
     </row>
     <row r="29">
@@ -1366,10 +1367,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>25640944</v>
+        <v>55181305</v>
       </c>
       <c r="C29" t="n">
-        <v>3165270</v>
+        <v>6092933</v>
       </c>
     </row>
     <row r="30">
@@ -1377,10 +1378,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>28572276</v>
+        <v>72766813</v>
       </c>
       <c r="C30" t="n">
-        <v>3397678</v>
+        <v>7089311</v>
       </c>
     </row>
     <row r="31">
@@ -1388,10 +1389,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>32339619</v>
+        <v>96952838</v>
       </c>
       <c r="C31" t="n">
-        <v>3643466</v>
+        <v>8360548</v>
       </c>
     </row>
     <row r="32">
@@ -1399,10 +1400,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>36720881</v>
+        <v>123532435</v>
       </c>
       <c r="C32" t="n">
-        <v>3924632</v>
+        <v>10151237</v>
       </c>
     </row>
     <row r="33">
@@ -1410,10 +1411,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>42254977</v>
+        <v>144864062</v>
       </c>
       <c r="C33" t="n">
-        <v>4205621</v>
+        <v>11956822</v>
       </c>
     </row>
     <row r="34">
@@ -1421,10 +1422,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>49356295</v>
+        <v>159301417</v>
       </c>
       <c r="C34" t="n">
-        <v>4538155</v>
+        <v>13713720</v>
       </c>
     </row>
     <row r="35">
@@ -1432,10 +1433,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>58451018</v>
+        <v>166946913</v>
       </c>
       <c r="C35" t="n">
-        <v>4960204</v>
+        <v>15830103</v>
       </c>
     </row>
     <row r="36">
@@ -1443,10 +1444,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>74395856</v>
+        <v>173630573</v>
       </c>
       <c r="C36" t="n">
-        <v>5720828</v>
+        <v>18813600</v>
       </c>
     </row>
     <row r="37">
@@ -1454,10 +1455,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>100666451</v>
+        <v>177337559</v>
       </c>
       <c r="C37" t="n">
-        <v>6719463</v>
+        <v>23377641</v>
       </c>
     </row>
     <row r="38">
@@ -1465,10 +1466,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>129553694</v>
+        <v>177591882</v>
       </c>
       <c r="C38" t="n">
-        <v>7897677</v>
+        <v>29366770</v>
       </c>
     </row>
     <row r="39">
@@ -1476,10 +1477,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>151978597</v>
+        <v>170330008</v>
       </c>
       <c r="C39" t="n">
-        <v>9310681</v>
+        <v>35560414</v>
       </c>
     </row>
     <row r="40">
@@ -1487,10 +1488,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>167201426</v>
+        <v>157171135</v>
       </c>
       <c r="C40" t="n">
-        <v>10683942</v>
+        <v>40688654</v>
       </c>
     </row>
     <row r="41">
@@ -1498,10 +1499,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>175435903</v>
+        <v>146620094</v>
       </c>
       <c r="C41" t="n">
-        <v>12449262</v>
+        <v>43457213</v>
       </c>
     </row>
     <row r="42">
@@ -1509,10 +1510,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>179300102</v>
+        <v>139158123</v>
       </c>
       <c r="C42" t="n">
-        <v>14231398</v>
+        <v>44590583</v>
       </c>
     </row>
     <row r="43">
@@ -1520,10 +1521,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>180661404</v>
+        <v>133862521</v>
       </c>
       <c r="C43" t="n">
-        <v>16700539</v>
+        <v>44933634</v>
       </c>
     </row>
     <row r="44">
@@ -1531,10 +1532,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>178381725</v>
+        <v>128956223</v>
       </c>
       <c r="C44" t="n">
-        <v>19900115</v>
+        <v>45218131</v>
       </c>
     </row>
     <row r="45">
@@ -1542,10 +1543,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>171001294</v>
+        <v>125273099</v>
       </c>
       <c r="C45" t="n">
-        <v>24047532</v>
+        <v>45190804</v>
       </c>
     </row>
     <row r="46">
@@ -1553,10 +1554,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>155177174</v>
+        <v>122063154</v>
       </c>
       <c r="C46" t="n">
-        <v>28288814</v>
+        <v>45328864</v>
       </c>
     </row>
     <row r="47">
@@ -1564,10 +1565,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>138121669</v>
+        <v>118336547</v>
       </c>
       <c r="C47" t="n">
-        <v>31422510</v>
+        <v>45302820</v>
       </c>
     </row>
     <row r="48">
@@ -1575,10 +1576,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>126388066</v>
+        <v>116141323</v>
       </c>
       <c r="C48" t="n">
-        <v>33298574</v>
+        <v>45194097</v>
       </c>
     </row>
     <row r="49">
@@ -1586,10 +1587,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>118358175</v>
+        <v>114338116</v>
       </c>
       <c r="C49" t="n">
-        <v>34090676</v>
+        <v>44797107</v>
       </c>
     </row>
     <row r="50">
@@ -1597,10 +1598,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>113051080</v>
+        <v>113519152</v>
       </c>
       <c r="C50" t="n">
-        <v>34627571</v>
+        <v>44301276</v>
       </c>
     </row>
     <row r="51">
@@ -1608,10 +1609,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>108018080</v>
+        <v>112203891</v>
       </c>
       <c r="C51" t="n">
-        <v>34869216</v>
+        <v>44009511</v>
       </c>
     </row>
     <row r="52">
@@ -1619,10 +1620,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>103835565</v>
+        <v>111268948</v>
       </c>
       <c r="C52" t="n">
-        <v>35125890</v>
+        <v>43698477</v>
       </c>
     </row>
     <row r="53">
@@ -1630,10 +1631,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>100189115</v>
+        <v>110687793</v>
       </c>
       <c r="C53" t="n">
-        <v>35211205</v>
+        <v>43267992</v>
       </c>
     </row>
     <row r="54">
@@ -1641,10 +1642,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>96867207</v>
+        <v>109597242</v>
       </c>
       <c r="C54" t="n">
-        <v>35270963</v>
+        <v>42898915</v>
       </c>
     </row>
     <row r="55">
@@ -1652,10 +1653,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>94189405</v>
+        <v>108602518</v>
       </c>
       <c r="C55" t="n">
-        <v>35012845</v>
+        <v>42544097</v>
       </c>
     </row>
   </sheetData>
@@ -1689,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3447770</v>
+        <v>8633916</v>
       </c>
       <c r="C2" t="n">
-        <v>1358939</v>
+        <v>1666403</v>
       </c>
     </row>
     <row r="3">
@@ -1700,10 +1701,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3394202</v>
+        <v>8915648</v>
       </c>
       <c r="C3" t="n">
-        <v>1357158</v>
+        <v>1600976</v>
       </c>
     </row>
     <row r="4">
@@ -1711,10 +1712,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3522737</v>
+        <v>8984205</v>
       </c>
       <c r="C4" t="n">
-        <v>1383082</v>
+        <v>1609087</v>
       </c>
     </row>
     <row r="5">
@@ -1722,10 +1723,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3546847</v>
+        <v>9111980</v>
       </c>
       <c r="C5" t="n">
-        <v>1398179</v>
+        <v>1617339</v>
       </c>
     </row>
     <row r="6">
@@ -1733,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3610768</v>
+        <v>9313645</v>
       </c>
       <c r="C6" t="n">
-        <v>1428715</v>
+        <v>1627938</v>
       </c>
     </row>
     <row r="7">
@@ -1744,10 +1745,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3520647</v>
+        <v>9340130</v>
       </c>
       <c r="C7" t="n">
-        <v>1476885</v>
+        <v>1625599</v>
       </c>
     </row>
     <row r="8">
@@ -1755,10 +1756,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3613689</v>
+        <v>9511997</v>
       </c>
       <c r="C8" t="n">
-        <v>1512720</v>
+        <v>1625969</v>
       </c>
     </row>
     <row r="9">
@@ -1766,10 +1767,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3512363</v>
+        <v>9885746</v>
       </c>
       <c r="C9" t="n">
-        <v>1579063</v>
+        <v>1650609</v>
       </c>
     </row>
     <row r="10">
@@ -1777,10 +1778,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3568197</v>
+        <v>9893157</v>
       </c>
       <c r="C10" t="n">
-        <v>1613190</v>
+        <v>1678082</v>
       </c>
     </row>
     <row r="11">
@@ -1788,10 +1789,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3542160</v>
+        <v>10161888</v>
       </c>
       <c r="C11" t="n">
-        <v>1640130</v>
+        <v>1698929</v>
       </c>
     </row>
     <row r="12">
@@ -1799,10 +1800,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3542317</v>
+        <v>10548696</v>
       </c>
       <c r="C12" t="n">
-        <v>1690630</v>
+        <v>1745791</v>
       </c>
     </row>
     <row r="13">
@@ -1810,10 +1811,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3635863</v>
+        <v>10987637</v>
       </c>
       <c r="C13" t="n">
-        <v>1706138</v>
+        <v>1806375</v>
       </c>
     </row>
     <row r="14">
@@ -1821,10 +1822,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3661073</v>
+        <v>11353979</v>
       </c>
       <c r="C14" t="n">
-        <v>1741474</v>
+        <v>1862881</v>
       </c>
     </row>
     <row r="15">
@@ -1832,10 +1833,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3528959</v>
+        <v>11695615</v>
       </c>
       <c r="C15" t="n">
-        <v>1774499</v>
+        <v>1926638</v>
       </c>
     </row>
     <row r="16">
@@ -1843,10 +1844,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3538022</v>
+        <v>12033428</v>
       </c>
       <c r="C16" t="n">
-        <v>1843870</v>
+        <v>1949778</v>
       </c>
     </row>
     <row r="17">
@@ -1854,10 +1855,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3427663</v>
+        <v>12461227</v>
       </c>
       <c r="C17" t="n">
-        <v>1937445</v>
+        <v>1988555</v>
       </c>
     </row>
     <row r="18">
@@ -1865,10 +1866,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3468356</v>
+        <v>12922532</v>
       </c>
       <c r="C18" t="n">
-        <v>2040131</v>
+        <v>2040761</v>
       </c>
     </row>
     <row r="19">
@@ -1876,10 +1877,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3424339</v>
+        <v>13567693</v>
       </c>
       <c r="C19" t="n">
-        <v>2139059</v>
+        <v>2126196</v>
       </c>
     </row>
     <row r="20">
@@ -1887,10 +1888,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3530017</v>
+        <v>14482095</v>
       </c>
       <c r="C20" t="n">
-        <v>2241617</v>
+        <v>2221151</v>
       </c>
     </row>
     <row r="21">
@@ -1898,10 +1899,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3618626</v>
+        <v>15417124</v>
       </c>
       <c r="C21" t="n">
-        <v>2336114</v>
+        <v>2312595</v>
       </c>
     </row>
     <row r="22">
@@ -1909,10 +1910,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3553235</v>
+        <v>16394095</v>
       </c>
       <c r="C22" t="n">
-        <v>2446042</v>
+        <v>2412321</v>
       </c>
     </row>
     <row r="23">
@@ -1920,10 +1921,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3708962</v>
+        <v>17326904</v>
       </c>
       <c r="C23" t="n">
-        <v>2600375</v>
+        <v>2512685</v>
       </c>
     </row>
     <row r="24">
@@ -1931,10 +1932,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3936412</v>
+        <v>17696847</v>
       </c>
       <c r="C24" t="n">
-        <v>2817175</v>
+        <v>2565366</v>
       </c>
     </row>
     <row r="25">
@@ -1942,10 +1943,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>4010365</v>
+        <v>18846278</v>
       </c>
       <c r="C25" t="n">
-        <v>3049494</v>
+        <v>2629935</v>
       </c>
     </row>
     <row r="26">
@@ -1953,10 +1954,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>4260762</v>
+        <v>19845142</v>
       </c>
       <c r="C26" t="n">
-        <v>3345788</v>
+        <v>2724586</v>
       </c>
     </row>
     <row r="27">
@@ -1964,10 +1965,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>4526922</v>
+        <v>21283711</v>
       </c>
       <c r="C27" t="n">
-        <v>3597302</v>
+        <v>2807683</v>
       </c>
     </row>
     <row r="28">
@@ -1975,10 +1976,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>4767548</v>
+        <v>22847723</v>
       </c>
       <c r="C28" t="n">
-        <v>3824930</v>
+        <v>2976692</v>
       </c>
     </row>
     <row r="29">
@@ -1986,10 +1987,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>4761979</v>
+        <v>25640944</v>
       </c>
       <c r="C29" t="n">
-        <v>4035971</v>
+        <v>3165270</v>
       </c>
     </row>
     <row r="30">
@@ -1997,10 +1998,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>5104121</v>
+        <v>28572276</v>
       </c>
       <c r="C30" t="n">
-        <v>4310558</v>
+        <v>3397678</v>
       </c>
     </row>
     <row r="31">
@@ -2008,10 +2009,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>5381038</v>
+        <v>32339619</v>
       </c>
       <c r="C31" t="n">
-        <v>4719052</v>
+        <v>3643466</v>
       </c>
     </row>
     <row r="32">
@@ -2019,10 +2020,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>5965033</v>
+        <v>36720881</v>
       </c>
       <c r="C32" t="n">
-        <v>5133665</v>
+        <v>3924632</v>
       </c>
     </row>
     <row r="33">
@@ -2030,10 +2031,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>6888838</v>
+        <v>42254977</v>
       </c>
       <c r="C33" t="n">
-        <v>6073252</v>
+        <v>4205621</v>
       </c>
     </row>
     <row r="34">
@@ -2041,10 +2042,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>7986538</v>
+        <v>49356295</v>
       </c>
       <c r="C34" t="n">
-        <v>7514588</v>
+        <v>4538155</v>
       </c>
     </row>
     <row r="35">
@@ -2052,10 +2053,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>9457107</v>
+        <v>58451018</v>
       </c>
       <c r="C35" t="n">
-        <v>9367883</v>
+        <v>4960204</v>
       </c>
     </row>
     <row r="36">
@@ -2063,10 +2064,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>10410020</v>
+        <v>74395856</v>
       </c>
       <c r="C36" t="n">
-        <v>11139108</v>
+        <v>5720828</v>
       </c>
     </row>
     <row r="37">
@@ -2074,10 +2075,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>10974912</v>
+        <v>100666451</v>
       </c>
       <c r="C37" t="n">
-        <v>13234318</v>
+        <v>6719463</v>
       </c>
     </row>
     <row r="38">
@@ -2085,10 +2086,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>11197461</v>
+        <v>129553694</v>
       </c>
       <c r="C38" t="n">
-        <v>16524388</v>
+        <v>7897677</v>
       </c>
     </row>
     <row r="39">
@@ -2096,10 +2097,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>10749595</v>
+        <v>151978597</v>
       </c>
       <c r="C39" t="n">
-        <v>19974076</v>
+        <v>9310681</v>
       </c>
     </row>
     <row r="40">
@@ -2107,10 +2108,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>10061714</v>
+        <v>167201426</v>
       </c>
       <c r="C40" t="n">
-        <v>23049297</v>
+        <v>10683942</v>
       </c>
     </row>
     <row r="41">
@@ -2118,10 +2119,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>9258076</v>
+        <v>175435903</v>
       </c>
       <c r="C41" t="n">
-        <v>25650711</v>
+        <v>12449262</v>
       </c>
     </row>
     <row r="42">
@@ -2129,10 +2130,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>8636644</v>
+        <v>179300102</v>
       </c>
       <c r="C42" t="n">
-        <v>27244860</v>
+        <v>14231398</v>
       </c>
     </row>
     <row r="43">
@@ -2140,10 +2141,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>8311926</v>
+        <v>180661404</v>
       </c>
       <c r="C43" t="n">
-        <v>28061814</v>
+        <v>16700539</v>
       </c>
     </row>
     <row r="44">
@@ -2151,10 +2152,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>8458713</v>
+        <v>178381725</v>
       </c>
       <c r="C44" t="n">
-        <v>28323699</v>
+        <v>19900115</v>
       </c>
     </row>
     <row r="45">
@@ -2162,10 +2163,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>8032729</v>
+        <v>171001294</v>
       </c>
       <c r="C45" t="n">
-        <v>28496961</v>
+        <v>24047532</v>
       </c>
     </row>
     <row r="46">
@@ -2173,10 +2174,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>7916896</v>
+        <v>155177174</v>
       </c>
       <c r="C46" t="n">
-        <v>28627075</v>
+        <v>28288814</v>
       </c>
     </row>
     <row r="47">
@@ -2184,10 +2185,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>7909975</v>
+        <v>138121669</v>
       </c>
       <c r="C47" t="n">
-        <v>28820268</v>
+        <v>31422510</v>
       </c>
     </row>
     <row r="48">
@@ -2195,10 +2196,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>7805747</v>
+        <v>126388066</v>
       </c>
       <c r="C48" t="n">
-        <v>28894083</v>
+        <v>33298574</v>
       </c>
     </row>
     <row r="49">
@@ -2206,10 +2207,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>7955518</v>
+        <v>118358175</v>
       </c>
       <c r="C49" t="n">
-        <v>28987650</v>
+        <v>34090676</v>
       </c>
     </row>
     <row r="50">
@@ -2217,10 +2218,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>7633741</v>
+        <v>113051080</v>
       </c>
       <c r="C50" t="n">
-        <v>28991721</v>
+        <v>34627571</v>
       </c>
     </row>
     <row r="51">
@@ -2228,10 +2229,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>7653233</v>
+        <v>108018080</v>
       </c>
       <c r="C51" t="n">
-        <v>28891036</v>
+        <v>34869216</v>
       </c>
     </row>
     <row r="52">
@@ -2239,10 +2240,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>7506881</v>
+        <v>103835565</v>
       </c>
       <c r="C52" t="n">
-        <v>28763675</v>
+        <v>35125890</v>
       </c>
     </row>
     <row r="53">
@@ -2250,10 +2251,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>7410463</v>
+        <v>100189115</v>
       </c>
       <c r="C53" t="n">
-        <v>28707397</v>
+        <v>35211205</v>
       </c>
     </row>
     <row r="54">
@@ -2261,10 +2262,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>7276663</v>
+        <v>96867207</v>
       </c>
       <c r="C54" t="n">
-        <v>28561774</v>
+        <v>35270963</v>
       </c>
     </row>
     <row r="55">
@@ -2272,10 +2273,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>7344248</v>
+        <v>94189405</v>
       </c>
       <c r="C55" t="n">
-        <v>28515581</v>
+        <v>35012845</v>
       </c>
     </row>
   </sheetData>
@@ -2309,10 +2310,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3006059</v>
+        <v>3447770</v>
       </c>
       <c r="C2" t="n">
-        <v>1668807</v>
+        <v>1358939</v>
       </c>
     </row>
     <row r="3">
@@ -2320,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2919862</v>
+        <v>3394202</v>
       </c>
       <c r="C3" t="n">
-        <v>1670392</v>
+        <v>1357158</v>
       </c>
     </row>
     <row r="4">
@@ -2331,10 +2332,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3083099</v>
+        <v>3522737</v>
       </c>
       <c r="C4" t="n">
-        <v>1713645</v>
+        <v>1383082</v>
       </c>
     </row>
     <row r="5">
@@ -2342,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2957712</v>
+        <v>3546847</v>
       </c>
       <c r="C5" t="n">
-        <v>1746276</v>
+        <v>1398179</v>
       </c>
     </row>
     <row r="6">
@@ -2353,10 +2354,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3072750</v>
+        <v>3610768</v>
       </c>
       <c r="C6" t="n">
-        <v>1765710</v>
+        <v>1428715</v>
       </c>
     </row>
     <row r="7">
@@ -2364,10 +2365,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3219465</v>
+        <v>3520647</v>
       </c>
       <c r="C7" t="n">
-        <v>1801716</v>
+        <v>1476885</v>
       </c>
     </row>
     <row r="8">
@@ -2375,10 +2376,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3214309</v>
+        <v>3613689</v>
       </c>
       <c r="C8" t="n">
-        <v>1825252</v>
+        <v>1512720</v>
       </c>
     </row>
     <row r="9">
@@ -2386,10 +2387,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3080901</v>
+        <v>3512363</v>
       </c>
       <c r="C9" t="n">
-        <v>1858658</v>
+        <v>1579063</v>
       </c>
     </row>
     <row r="10">
@@ -2397,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3003397</v>
+        <v>3568197</v>
       </c>
       <c r="C10" t="n">
-        <v>1923176</v>
+        <v>1613190</v>
       </c>
     </row>
     <row r="11">
@@ -2408,10 +2409,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3286169</v>
+        <v>3542160</v>
       </c>
       <c r="C11" t="n">
-        <v>1987402</v>
+        <v>1640130</v>
       </c>
     </row>
     <row r="12">
@@ -2419,10 +2420,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3357051</v>
+        <v>3542317</v>
       </c>
       <c r="C12" t="n">
-        <v>2069373</v>
+        <v>1690630</v>
       </c>
     </row>
     <row r="13">
@@ -2430,10 +2431,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3267027</v>
+        <v>3635863</v>
       </c>
       <c r="C13" t="n">
-        <v>2141582</v>
+        <v>1706138</v>
       </c>
     </row>
     <row r="14">
@@ -2441,10 +2442,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3252461</v>
+        <v>3661073</v>
       </c>
       <c r="C14" t="n">
-        <v>2222563</v>
+        <v>1741474</v>
       </c>
     </row>
     <row r="15">
@@ -2452,10 +2453,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3286400</v>
+        <v>3528959</v>
       </c>
       <c r="C15" t="n">
-        <v>2299172</v>
+        <v>1774499</v>
       </c>
     </row>
     <row r="16">
@@ -2463,10 +2464,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3418004</v>
+        <v>3538022</v>
       </c>
       <c r="C16" t="n">
-        <v>2365325</v>
+        <v>1843870</v>
       </c>
     </row>
     <row r="17">
@@ -2474,10 +2475,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3475317</v>
+        <v>3427663</v>
       </c>
       <c r="C17" t="n">
-        <v>2449130</v>
+        <v>1937445</v>
       </c>
     </row>
     <row r="18">
@@ -2485,10 +2486,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3384322</v>
+        <v>3468356</v>
       </c>
       <c r="C18" t="n">
-        <v>2563738</v>
+        <v>2040131</v>
       </c>
     </row>
     <row r="19">
@@ -2496,10 +2497,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3455410</v>
+        <v>3424339</v>
       </c>
       <c r="C19" t="n">
-        <v>2721259</v>
+        <v>2139059</v>
       </c>
     </row>
     <row r="20">
@@ -2507,10 +2508,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3594096</v>
+        <v>3530017</v>
       </c>
       <c r="C20" t="n">
-        <v>2903846</v>
+        <v>2241617</v>
       </c>
     </row>
     <row r="21">
@@ -2518,10 +2519,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>3699275</v>
+        <v>3618626</v>
       </c>
       <c r="C21" t="n">
-        <v>3105329</v>
+        <v>2336114</v>
       </c>
     </row>
     <row r="22">
@@ -2529,10 +2530,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>3746874</v>
+        <v>3553235</v>
       </c>
       <c r="C22" t="n">
-        <v>3251631</v>
+        <v>2446042</v>
       </c>
     </row>
     <row r="23">
@@ -2540,10 +2541,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>3737886</v>
+        <v>3708962</v>
       </c>
       <c r="C23" t="n">
-        <v>3372458</v>
+        <v>2600375</v>
       </c>
     </row>
     <row r="24">
@@ -2551,10 +2552,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>3629943</v>
+        <v>3936412</v>
       </c>
       <c r="C24" t="n">
-        <v>3571051</v>
+        <v>2817175</v>
       </c>
     </row>
     <row r="25">
@@ -2562,10 +2563,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>3819798</v>
+        <v>4010365</v>
       </c>
       <c r="C25" t="n">
-        <v>3704967</v>
+        <v>3049494</v>
       </c>
     </row>
     <row r="26">
@@ -2573,10 +2574,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>3930959</v>
+        <v>4260762</v>
       </c>
       <c r="C26" t="n">
-        <v>3935650</v>
+        <v>3345788</v>
       </c>
     </row>
     <row r="27">
@@ -2584,10 +2585,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>4148157</v>
+        <v>4526922</v>
       </c>
       <c r="C27" t="n">
-        <v>4289859</v>
+        <v>3597302</v>
       </c>
     </row>
     <row r="28">
@@ -2595,10 +2596,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>4408824</v>
+        <v>4767548</v>
       </c>
       <c r="C28" t="n">
-        <v>4749525</v>
+        <v>3824930</v>
       </c>
     </row>
     <row r="29">
@@ -2606,10 +2607,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>4930835</v>
+        <v>4761979</v>
       </c>
       <c r="C29" t="n">
-        <v>5321209</v>
+        <v>4035971</v>
       </c>
     </row>
     <row r="30">
@@ -2617,10 +2618,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>5618993</v>
+        <v>5104121</v>
       </c>
       <c r="C30" t="n">
-        <v>5924756</v>
+        <v>4310558</v>
       </c>
     </row>
     <row r="31">
@@ -2628,10 +2629,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>6207148</v>
+        <v>5381038</v>
       </c>
       <c r="C31" t="n">
-        <v>6667922</v>
+        <v>4719052</v>
       </c>
     </row>
     <row r="32">
@@ -2639,10 +2640,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>7130104</v>
+        <v>5965033</v>
       </c>
       <c r="C32" t="n">
-        <v>7436238</v>
+        <v>5133665</v>
       </c>
     </row>
     <row r="33">
@@ -2650,10 +2651,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>8396265</v>
+        <v>6888838</v>
       </c>
       <c r="C33" t="n">
-        <v>8615177</v>
+        <v>6073252</v>
       </c>
     </row>
     <row r="34">
@@ -2661,10 +2662,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>9982452</v>
+        <v>7986538</v>
       </c>
       <c r="C34" t="n">
-        <v>10119184</v>
+        <v>7514588</v>
       </c>
     </row>
     <row r="35">
@@ -2672,10 +2673,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>11708697</v>
+        <v>9457107</v>
       </c>
       <c r="C35" t="n">
-        <v>12935894</v>
+        <v>9367883</v>
       </c>
     </row>
     <row r="36">
@@ -2683,10 +2684,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>13429729</v>
+        <v>10410020</v>
       </c>
       <c r="C36" t="n">
-        <v>17011460</v>
+        <v>11139108</v>
       </c>
     </row>
     <row r="37">
@@ -2694,10 +2695,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>14279037</v>
+        <v>10974912</v>
       </c>
       <c r="C37" t="n">
-        <v>22318781</v>
+        <v>13234318</v>
       </c>
     </row>
     <row r="38">
@@ -2705,10 +2706,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>14422221</v>
+        <v>11197461</v>
       </c>
       <c r="C38" t="n">
-        <v>27478800</v>
+        <v>16524388</v>
       </c>
     </row>
     <row r="39">
@@ -2716,10 +2717,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>14036326</v>
+        <v>10749595</v>
       </c>
       <c r="C39" t="n">
-        <v>31530926</v>
+        <v>19974076</v>
       </c>
     </row>
     <row r="40">
@@ -2727,10 +2728,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>13499802</v>
+        <v>10061714</v>
       </c>
       <c r="C40" t="n">
-        <v>34601383</v>
+        <v>23049297</v>
       </c>
     </row>
     <row r="41">
@@ -2738,10 +2739,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>13093193</v>
+        <v>9258076</v>
       </c>
       <c r="C41" t="n">
-        <v>36770543</v>
+        <v>25650711</v>
       </c>
     </row>
     <row r="42">
@@ -2749,10 +2750,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>12819923</v>
+        <v>8636644</v>
       </c>
       <c r="C42" t="n">
-        <v>38810033</v>
+        <v>27244860</v>
       </c>
     </row>
     <row r="43">
@@ -2760,10 +2761,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>12131262</v>
+        <v>8311926</v>
       </c>
       <c r="C43" t="n">
-        <v>40308176</v>
+        <v>28061814</v>
       </c>
     </row>
     <row r="44">
@@ -2771,10 +2772,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>11405485</v>
+        <v>8458713</v>
       </c>
       <c r="C44" t="n">
-        <v>41103079</v>
+        <v>28323699</v>
       </c>
     </row>
     <row r="45">
@@ -2782,10 +2783,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>11256267</v>
+        <v>8032729</v>
       </c>
       <c r="C45" t="n">
-        <v>41669986</v>
+        <v>28496961</v>
       </c>
     </row>
     <row r="46">
@@ -2793,10 +2794,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>11065442</v>
+        <v>7916896</v>
       </c>
       <c r="C46" t="n">
-        <v>42055359</v>
+        <v>28627075</v>
       </c>
     </row>
     <row r="47">
@@ -2804,10 +2805,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>10853627</v>
+        <v>7909975</v>
       </c>
       <c r="C47" t="n">
-        <v>42286164</v>
+        <v>28820268</v>
       </c>
     </row>
     <row r="48">
@@ -2815,10 +2816,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>11019619</v>
+        <v>7805747</v>
       </c>
       <c r="C48" t="n">
-        <v>42380837</v>
+        <v>28894083</v>
       </c>
     </row>
     <row r="49">
@@ -2826,10 +2827,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>10783255</v>
+        <v>7955518</v>
       </c>
       <c r="C49" t="n">
-        <v>42281282</v>
+        <v>28987650</v>
       </c>
     </row>
     <row r="50">
@@ -2837,10 +2838,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>10598836</v>
+        <v>7633741</v>
       </c>
       <c r="C50" t="n">
-        <v>42054985</v>
+        <v>28991721</v>
       </c>
     </row>
     <row r="51">
@@ -2848,10 +2849,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>10492693</v>
+        <v>7653233</v>
       </c>
       <c r="C51" t="n">
-        <v>41785084</v>
+        <v>28891036</v>
       </c>
     </row>
     <row r="52">
@@ -2859,10 +2860,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>10534337</v>
+        <v>7506881</v>
       </c>
       <c r="C52" t="n">
-        <v>41592229</v>
+        <v>28763675</v>
       </c>
     </row>
     <row r="53">
@@ -2870,10 +2871,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>10508284</v>
+        <v>7410463</v>
       </c>
       <c r="C53" t="n">
-        <v>41293037</v>
+        <v>28707397</v>
       </c>
     </row>
     <row r="54">
@@ -2881,10 +2882,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>10427893</v>
+        <v>7276663</v>
       </c>
       <c r="C54" t="n">
-        <v>41001390</v>
+        <v>28561774</v>
       </c>
     </row>
     <row r="55">
@@ -2892,10 +2893,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>10291494</v>
+        <v>7344248</v>
       </c>
       <c r="C55" t="n">
-        <v>40710151</v>
+        <v>28515581</v>
       </c>
     </row>
   </sheetData>
@@ -2929,6 +2930,626 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
+        <v>3006059</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1668807</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2919862</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1670392</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3083099</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1713645</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2957712</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1746276</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3072750</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1765710</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3219465</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1801716</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3214309</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1825252</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3080901</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1858658</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3003397</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1923176</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3286169</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1987402</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3357051</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2069373</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3267027</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2141582</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3252461</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2222563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3286400</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2299172</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3418004</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2365325</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3475317</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2449130</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3384322</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2563738</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3455410</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2721259</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3594096</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2903846</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3699275</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3105329</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3746874</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3251631</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3737886</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3372458</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3629943</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3571051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3819798</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3704967</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3930959</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3935650</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4148157</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4289859</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>4408824</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4749525</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4930835</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5321209</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5618993</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5924756</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6207148</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6667922</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>7130104</v>
+      </c>
+      <c r="C32" t="n">
+        <v>7436238</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8396265</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8615177</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>9982452</v>
+      </c>
+      <c r="C34" t="n">
+        <v>10119184</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11708697</v>
+      </c>
+      <c r="C35" t="n">
+        <v>12935894</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>13429729</v>
+      </c>
+      <c r="C36" t="n">
+        <v>17011460</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>14279037</v>
+      </c>
+      <c r="C37" t="n">
+        <v>22318781</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>14422221</v>
+      </c>
+      <c r="C38" t="n">
+        <v>27478800</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>14036326</v>
+      </c>
+      <c r="C39" t="n">
+        <v>31530926</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>13499802</v>
+      </c>
+      <c r="C40" t="n">
+        <v>34601383</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>13093193</v>
+      </c>
+      <c r="C41" t="n">
+        <v>36770543</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>12819923</v>
+      </c>
+      <c r="C42" t="n">
+        <v>38810033</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>12131262</v>
+      </c>
+      <c r="C43" t="n">
+        <v>40308176</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>11405485</v>
+      </c>
+      <c r="C44" t="n">
+        <v>41103079</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>11256267</v>
+      </c>
+      <c r="C45" t="n">
+        <v>41669986</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>11065442</v>
+      </c>
+      <c r="C46" t="n">
+        <v>42055359</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>10853627</v>
+      </c>
+      <c r="C47" t="n">
+        <v>42286164</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>11019619</v>
+      </c>
+      <c r="C48" t="n">
+        <v>42380837</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>10783255</v>
+      </c>
+      <c r="C49" t="n">
+        <v>42281282</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>10598836</v>
+      </c>
+      <c r="C50" t="n">
+        <v>42054985</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>10492693</v>
+      </c>
+      <c r="C51" t="n">
+        <v>41785084</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>10534337</v>
+      </c>
+      <c r="C52" t="n">
+        <v>41592229</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>10508284</v>
+      </c>
+      <c r="C53" t="n">
+        <v>41293037</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>10427893</v>
+      </c>
+      <c r="C54" t="n">
+        <v>41001390</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>10291494</v>
+      </c>
+      <c r="C55" t="n">
+        <v>40710151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ebba</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>2934338</v>
       </c>
       <c r="C2" t="n">
